--- a/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_394_R43.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/individual/NP_play_by_play_EL_394_R43.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.574299999999999</v>
+        <v>8.479200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2452</v>
+        <v>3.5056</v>
       </c>
       <c r="F2" t="n">
-        <v>5.3291</v>
+        <v>4.9736</v>
       </c>
       <c r="G2" t="n">
         <v>4.8289</v>
@@ -610,13 +610,13 @@
         <v>2.7297</v>
       </c>
       <c r="S2" t="n">
-        <v>1.427</v>
+        <v>1.3318</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4188</v>
+        <v>-0.1584</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8458</v>
+        <v>1.4903</v>
       </c>
       <c r="V2" t="n">
         <v>1.8635</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2109</v>
+        <v>4.2339</v>
       </c>
       <c r="E3" t="n">
-        <v>0.73</v>
+        <v>0.1733</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4808</v>
+        <v>4.0607</v>
       </c>
       <c r="G3" t="n">
         <v>1.6567</v>
@@ -688,13 +688,13 @@
         <v>2.0473</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5332</v>
+        <v>1.5563</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5749</v>
+        <v>0.0181</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9583</v>
+        <v>1.5382</v>
       </c>
       <c r="V3" t="n">
         <v>1.2485</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2743</v>
+        <v>3.2043</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7321</v>
+        <v>-0.7052</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0064</v>
+        <v>3.9094</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1117</v>
@@ -766,13 +766,13 @@
         <v>2.0473</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0247</v>
+        <v>0.9547</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2752</v>
+        <v>-0.2483</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2999</v>
+        <v>1.2029</v>
       </c>
       <c r="V4" t="n">
         <v>4.5888</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8181</v>
+        <v>2.6604</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5357</v>
+        <v>0.048</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3538</v>
+        <v>2.6124</v>
       </c>
       <c r="G5" t="n">
         <v>1.1163</v>
@@ -844,13 +844,13 @@
         <v>1.8198</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1389</v>
+        <v>0.7033</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9217</v>
+        <v>-0.3381</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7828000000000001</v>
+        <v>1.0414</v>
       </c>
       <c r="V5" t="n">
         <v>0.1583</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0076</v>
+        <v>2.0186</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8884</v>
+        <v>-2.3945</v>
       </c>
       <c r="F6" t="n">
-        <v>3.896</v>
+        <v>4.4131</v>
       </c>
       <c r="G6" t="n">
         <v>2.1785</v>
@@ -922,13 +922,13 @@
         <v>2.2747</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3975</v>
+        <v>0.6135</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9816</v>
+        <v>-0.4877</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5841</v>
+        <v>1.1012</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7734</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2787</v>
+        <v>0.3954</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2236</v>
+        <v>-0.1068</v>
       </c>
       <c r="F7" t="n">
         <v>0.5022</v>
@@ -1000,10 +1000,10 @@
         <v>0.4549</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0718</v>
+        <v>0.0449</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2753</v>
+        <v>-0.1586</v>
       </c>
       <c r="U7" t="n">
         <v>0.2035</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2672</v>
+        <v>-0.2348</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0718</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1953</v>
+        <v>-0.163</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2169</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0503</v>
+        <v>-0.018</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0718</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0215</v>
+        <v>0.0539</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5138</v>
+        <v>-0.397</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0772</v>
+        <v>0.0395</v>
       </c>
       <c r="F9" t="n">
         <v>-0.4366</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2395</v>
+        <v>-0.1227</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2873</v>
+        <v>-0.1706</v>
       </c>
       <c r="U9" t="n">
         <v>0.0478</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0195</v>
+        <v>-1.3051</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7682</v>
+        <v>0.418</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7878</v>
+        <v>-1.7231</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9184</v>
@@ -1234,13 +1234,13 @@
         <v>0.4549</v>
       </c>
       <c r="S10" t="n">
-        <v>0.534</v>
+        <v>0.2485</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6466</v>
+        <v>0.2964</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1126</v>
+        <v>-0.0479</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0901</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8284</v>
+        <v>-3.1463</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4425</v>
+        <v>-2.7927</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3859</v>
+        <v>-0.3536</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6557</v>
@@ -1312,13 +1312,13 @@
         <v>0.6824</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4407</v>
+        <v>0.1228</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3713</v>
+        <v>0.0211</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0694</v>
+        <v>0.1017</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1583</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6576</v>
+        <v>-5.3128</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2104</v>
+        <v>-5.8333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5528</v>
+        <v>0.5205</v>
       </c>
       <c r="G12" t="n">
         <v>-5.724</v>
@@ -1390,13 +1390,13 @@
         <v>1.1374</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.273</v>
+        <v>0.0718</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6943</v>
+        <v>-0.3171</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4213</v>
+        <v>0.3889</v>
       </c>
       <c r="V12" t="n">
         <v>1.4768</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.877399999999998</v>
+        <v>10.5958</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.438299999999998</v>
+        <v>-7.719900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>18.3155</v>
+        <v>18.3156</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3834</v>
@@ -1468,13 +1468,13 @@
         <v>13.6484</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7886</v>
+        <v>5.5069</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3332</v>
+        <v>-1.615</v>
       </c>
       <c r="U13" t="n">
-        <v>7.1218</v>
+        <v>7.1219</v>
       </c>
       <c r="V13" t="n">
         <v>7.4724</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2182</v>
+        <v>1.7882</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6335</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5847</v>
+        <v>2.6314</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2139</v>
+        <v>1.0908</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1578</v>
+        <v>-0.1028</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3717</v>
+        <v>1.1936</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3005</v>
+        <v>0.9827</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6439</v>
+        <v>0.4448</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3434</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5145</v>
+        <v>0.1082</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5138</v>
+        <v>-0.5476</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0283</v>
+        <v>0.6558</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6824</v>
+        <v>0.4549</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6824</v>
+        <v>1.5923</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3218</v>
+        <v>0.2425</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9340000000000001</v>
+        <v>-0.8468</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3878</v>
+        <v>1.0893</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1583</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4671</v>
+        <v>1.6916</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.2603</v>
+        <v>0.6762</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7273</v>
+        <v>1.0153</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1217</v>
+        <v>1.3407</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4876</v>
+        <v>1.1585</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3659</v>
+        <v>0.1822</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3079</v>
+        <v>1.2532</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8626</v>
+        <v>1.1042</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5547</v>
+        <v>0.149</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1862</v>
+        <v>0.0876</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3751</v>
+        <v>0.0544</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1888</v>
+        <v>0.0332</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2275</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.1374</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3648</v>
+        <v>0.9099</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5029</v>
+        <v>-0.5118</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4308</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9337</v>
+        <v>0.0179</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6151</v>
+        <v>1.0901</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0901</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4499</v>
+        <v>1.6536</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1934</v>
+        <v>-0.1837</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6434</v>
+        <v>1.8373</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0908</v>
+        <v>0.2139</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1028</v>
+        <v>-1.1578</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1936</v>
+        <v>1.3717</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9827</v>
+        <v>-0.3005</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4448</v>
+        <v>-0.6439</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.3434</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1082</v>
+        <v>0.5145</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5476</v>
+        <v>-0.5138</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6558</v>
+        <v>1.0283</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4549</v>
+        <v>0.6824</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5923</v>
+        <v>0.6824</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0958</v>
+        <v>0.7573</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1971</v>
+        <v>0.1169</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1012</v>
+        <v>0.6404</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3902</v>
+        <v>1.2276</v>
       </c>
       <c r="E17" t="n">
-        <v>1.725</v>
+        <v>-1.4937</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3349</v>
+        <v>2.7214</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2555</v>
+        <v>0.1217</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.848</v>
+        <v>0.4876</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1035</v>
+        <v>-0.3659</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2792</v>
+        <v>0.3079</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1072</v>
+        <v>0.8626</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3865</v>
+        <v>-0.5547</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0237</v>
+        <v>-0.1862</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7407</v>
+        <v>-0.3751</v>
       </c>
       <c r="O17" t="n">
-        <v>0.717</v>
+        <v>0.1888</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9099</v>
+        <v>0.2275</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1374</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9099</v>
+        <v>1.3648</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7016</v>
+        <v>0.2634</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2874</v>
+        <v>-0.6643</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4142</v>
+        <v>0.9277</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4768</v>
+        <v>0.6151</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1583</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6352</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2312</v>
+        <v>1.2154</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5595</v>
+        <v>1.4916</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6717</v>
+        <v>-0.2762</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3407</v>
+        <v>1.2555</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1585</v>
+        <v>-0.848</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1822</v>
+        <v>2.1035</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2532</v>
+        <v>1.2792</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1042</v>
+        <v>-0.1072</v>
       </c>
       <c r="L18" t="n">
-        <v>0.149</v>
+        <v>1.3865</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0876</v>
+        <v>-0.0237</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0544</v>
+        <v>-0.7407</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0332</v>
+        <v>0.717</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2275</v>
+        <v>0.9099</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1374</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.9099</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9722</v>
+        <v>0.5268</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6464</v>
+        <v>0.054</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3257</v>
+        <v>0.4728</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0901</v>
+        <v>-1.4768</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0901</v>
+        <v>0.1583</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6352</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8449</v>
+        <v>0.0165</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3408</v>
+        <v>-0.9906</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4959</v>
+        <v>1.0071</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2173</v>
@@ -1936,13 +1936,13 @@
         <v>1.3648</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.8341</v>
+        <v>-0.9727</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1372</v>
+        <v>-0.787</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6969</v>
+        <v>-0.1857</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1583</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2138</v>
+        <v>-0.5846</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.801</v>
+        <v>-2.4508</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5873</v>
+        <v>1.8663</v>
       </c>
       <c r="G20" t="n">
         <v>2.7039</v>
@@ -2014,13 +2014,13 @@
         <v>1.8198</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6201</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1971</v>
+        <v>-0.8468</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5769</v>
+        <v>0.8559</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7052</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.578</v>
+        <v>-0.8979</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3391</v>
+        <v>-0.1056</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2389</v>
+        <v>-0.7924</v>
       </c>
       <c r="G21" t="n">
         <v>0.4379</v>
@@ -2092,13 +2092,13 @@
         <v>0.9099</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2906</v>
+        <v>-0.6106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8619</v>
+        <v>-0.6284</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4287</v>
+        <v>0.0179</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6352</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.138</v>
+        <v>-2.2349</v>
       </c>
       <c r="E22" t="n">
         <v>-1.446</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.789</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8213</v>
@@ -2170,13 +2170,13 @@
         <v>0.6824</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3639</v>
+        <v>-0.4609</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5028</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1388</v>
+        <v>0.0419</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6352</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2504</v>
+        <v>-3.4794</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6539</v>
+        <v>-3.4204</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5966</v>
+        <v>-0.059</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6139</v>
@@ -2248,13 +2248,13 @@
         <v>2.0473</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9323</v>
+        <v>-1.1612</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.7837</v>
+        <v>-1.5502</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1486</v>
+        <v>0.3889</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4768</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.609</v>
+        <v>-7.9388</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.495799999999999</v>
+        <v>-8.846</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8868</v>
+        <v>0.9072</v>
       </c>
       <c r="G24" t="n">
         <v>-3.1283</v>
@@ -2326,13 +2326,13 @@
         <v>1.3648</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2059</v>
+        <v>-0.5357</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5865</v>
+        <v>-0.9367</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3805</v>
+        <v>0.4009</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0901</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.877500000000001</v>
+        <v>-7.5427</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.6123</v>
+        <v>-17.6122</v>
       </c>
       <c r="F25" t="n">
-        <v>7.734700000000001</v>
+        <v>10.0694</v>
       </c>
       <c r="G25" t="n">
-        <v>2.383600000000001</v>
+        <v>2.383599999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-4.7353</v>
@@ -2395,7 +2395,7 @@
         <v>3.4448</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q25" t="n">
         <v>-13.6485</v>
@@ -2404,13 +2404,13 @@
         <v>13.6483</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.788600000000001</v>
+        <v>-2.4539</v>
       </c>
       <c r="T25" t="n">
-        <v>-7.122100000000001</v>
+        <v>-7.1218</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3332</v>
+        <v>4.667899999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-7.4724</v>
